--- a/demo_data/sectors/perakende_eticaret/inventory.xlsx
+++ b/demo_data/sectors/perakende_eticaret/inventory.xlsx
@@ -482,7 +482,7 @@
         <v>2200</v>
       </c>
       <c r="E2" t="n">
-        <v>760892</v>
+        <v>760881.98</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>45827</v>
